--- a/artfynd/A 25936-2024 artfynd.xlsx
+++ b/artfynd/A 25936-2024 artfynd.xlsx
@@ -3126,7 +3126,7 @@
         <v>121783141</v>
       </c>
       <c r="B23" t="n">
-        <v>57510</v>
+        <v>57518</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 25936-2024 artfynd.xlsx
+++ b/artfynd/A 25936-2024 artfynd.xlsx
@@ -3126,7 +3126,7 @@
         <v>121783141</v>
       </c>
       <c r="B23" t="n">
-        <v>57518</v>
+        <v>57522</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 25936-2024 artfynd.xlsx
+++ b/artfynd/A 25936-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3231,6 +3231,117 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122650381</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97194</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Snäckedal, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>592451</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6376499</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-02-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25936-2024 artfynd.xlsx
+++ b/artfynd/A 25936-2024 artfynd.xlsx
@@ -3236,7 +3236,7 @@
         <v>122650381</v>
       </c>
       <c r="B24" t="n">
-        <v>97194</v>
+        <v>97195</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 25936-2024 artfynd.xlsx
+++ b/artfynd/A 25936-2024 artfynd.xlsx
@@ -3236,7 +3236,7 @@
         <v>122650381</v>
       </c>
       <c r="B24" t="n">
-        <v>97301</v>
+        <v>97309</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 25936-2024 artfynd.xlsx
+++ b/artfynd/A 25936-2024 artfynd.xlsx
@@ -3236,7 +3236,7 @@
         <v>122650381</v>
       </c>
       <c r="B24" t="n">
-        <v>97309</v>
+        <v>97311</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 25936-2024 artfynd.xlsx
+++ b/artfynd/A 25936-2024 artfynd.xlsx
@@ -3236,7 +3236,7 @@
         <v>122650381</v>
       </c>
       <c r="B24" t="n">
-        <v>97311</v>
+        <v>97319</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>

--- a/artfynd/A 25936-2024 artfynd.xlsx
+++ b/artfynd/A 25936-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3342,6 +3342,228 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123709446</v>
+      </c>
+      <c r="B25" t="n">
+        <v>96957</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Snäckedal, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>592447</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6376762</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123709566</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Snäckedal, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>592448</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6376747</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-29</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25936-2024 artfynd.xlsx
+++ b/artfynd/A 25936-2024 artfynd.xlsx
@@ -3344,10 +3344,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123709446</v>
+        <v>123709566</v>
       </c>
       <c r="B25" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3356,30 +3356,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592447</v>
+        <v>592448</v>
       </c>
       <c r="R25" t="n">
-        <v>6376762</v>
+        <v>6376747</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123709566</v>
+        <v>123709446</v>
       </c>
       <c r="B26" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3467,30 +3467,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592448</v>
+        <v>592447</v>
       </c>
       <c r="R26" t="n">
-        <v>6376747</v>
+        <v>6376762</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 25936-2024 artfynd.xlsx
+++ b/artfynd/A 25936-2024 artfynd.xlsx
@@ -3344,10 +3344,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123709566</v>
+        <v>123709446</v>
       </c>
       <c r="B25" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3356,30 +3356,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592448</v>
+        <v>592447</v>
       </c>
       <c r="R25" t="n">
-        <v>6376747</v>
+        <v>6376762</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123709446</v>
+        <v>123709566</v>
       </c>
       <c r="B26" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3467,30 +3467,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -3503,10 +3503,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592447</v>
+        <v>592448</v>
       </c>
       <c r="R26" t="n">
-        <v>6376762</v>
+        <v>6376747</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
